--- a/inst/resources/outputs_schema_data_analytics_mortality_roster_template.xlsx
+++ b/inst/resources/outputs_schema_data_analytics_mortality_roster_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A49D2CAF-DD7B-45CA-ADE4-BF96A94CBC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4984ACAB-D701-4D0A-A461-4C1307F26DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25560" yWindow="1980" windowWidth="24225" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -82,9 +82,6 @@
     <t>unweighted</t>
   </si>
   <si>
-    <t>data</t>
-  </si>
-  <si>
     <t>age_pyramid_overall_weighted</t>
   </si>
   <si>
@@ -206,6 +203,9 @@
   </si>
   <si>
     <t>variable=@variable_map$age_months_cat,stat_type="percentage",disaggregation=@variable_map$sex,variable_label=@variable_label$age_months_cat,disaggregation_wide=TRUE</t>
+  </si>
+  <si>
+    <t>base</t>
   </si>
 </sst>
 </file>
@@ -670,15 +670,15 @@
         <v>19</v>
       </c>
       <c r="K2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
         <v>15</v>
@@ -687,33 +687,33 @@
         <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K3" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
         <v>24</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>26</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>27</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
       </c>
       <c r="H4" t="s">
         <v>18</v>
@@ -722,50 +722,50 @@
         <v>19</v>
       </c>
       <c r="K4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
         <v>29</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
         <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" t="s">
-        <v>31</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
         <v>32</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
         <v>33</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>34</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="H6" t="s">
         <v>18</v>
@@ -774,189 +774,189 @@
         <v>19</v>
       </c>
       <c r="K6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
         <v>37</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="D7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="H7" t="s">
         <v>18</v>
       </c>
       <c r="I7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" t="s">
         <v>40</v>
       </c>
-      <c r="B8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>41</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" t="s">
         <v>43</v>
-      </c>
-      <c r="H8" t="s">
-        <v>44</v>
       </c>
       <c r="I8" t="s">
         <v>19</v>
       </c>
       <c r="K8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
         <v>46</v>
       </c>
-      <c r="B9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>47</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="H9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I9" t="s">
         <v>19</v>
       </c>
       <c r="K9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="H10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I10" t="s">
         <v>19</v>
       </c>
       <c r="K10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="H11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I11" t="s">
         <v>19</v>
       </c>
       <c r="K11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" t="s">
         <v>54</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="s">
         <v>55</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F12" t="s">
-        <v>48</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="H12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I12" t="s">
         <v>19</v>
       </c>
       <c r="K12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" t="s">
         <v>58</v>
       </c>
-      <c r="B13" t="s">
+      <c r="D13" t="s">
         <v>59</v>
       </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F13" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="H13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I13" t="s">
         <v>19</v>
       </c>
       <c r="K13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/inst/resources/outputs_schema_data_analytics_mortality_roster_template.xlsx
+++ b/inst/resources/outputs_schema_data_analytics_mortality_roster_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SaeedRAHMAN\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4984ACAB-D701-4D0A-A461-4C1307F26DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DCFC42-0F4A-4D8C-8B83-FA2285F8755D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25560" yWindow="1980" windowWidth="24225" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -596,8 +596,8 @@
     <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.85546875" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.42578125" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" customWidth="1"/>
     <col min="9" max="9" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
@@ -670,7 +670,7 @@
         <v>19</v>
       </c>
       <c r="K2" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
